--- a/diseases/d199/2010-2014.xlsx
+++ b/diseases/d199/2010-2014.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13195,7 +13195,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -16006,7 +16006,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -16943,7 +16943,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -18817,7 +18817,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -22565,7 +22565,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -23502,7 +23502,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -24439,7 +24439,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -27250,7 +27250,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -28187,7 +28187,7 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -29124,7 +29124,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -30061,7 +30061,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -30998,7 +30998,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -31935,7 +31935,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN168" t="b">
@@ -32872,7 +32872,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -33809,7 +33809,7 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN178" t="b">
@@ -34746,7 +34746,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -35683,7 +35683,7 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN188" t="b">
@@ -36620,7 +36620,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -37557,7 +37557,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -38494,7 +38494,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -39431,7 +39431,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -40368,7 +40368,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -41305,7 +41305,7 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN218" t="b">
@@ -42242,7 +42242,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -43179,7 +43179,7 @@
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN228" t="b">
@@ -44914,7 +44914,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -47447,7 +47447,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -50379,7 +50379,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -52912,7 +52912,7 @@
       </c>
       <c r="AM278" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN278" t="b">
@@ -55445,7 +55445,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -58377,7 +58377,7 @@
       </c>
       <c r="AM306" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN306" t="b">
@@ -60910,7 +60910,7 @@
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN319" t="b">
@@ -63443,7 +63443,7 @@
       </c>
       <c r="AM332" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN332" t="b">
@@ -66375,7 +66375,7 @@
       </c>
       <c r="AM347" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN347" t="b">
@@ -68908,7 +68908,7 @@
       </c>
       <c r="AM360" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN360" t="b">
@@ -71840,7 +71840,7 @@
       </c>
       <c r="AM375" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN375" t="b">
@@ -74373,7 +74373,7 @@
       </c>
       <c r="AM388" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN388" t="b">
@@ -76906,7 +76906,7 @@
       </c>
       <c r="AM401" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN401" t="b">
@@ -79838,7 +79838,7 @@
       </c>
       <c r="AM416" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN416" t="b">

--- a/diseases/d199/2010-2014.xlsx
+++ b/diseases/d199/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16933,7 +16933,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -17870,7 +17870,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18807,7 +18807,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21618,7 +21618,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22555,7 +22555,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23492,7 +23492,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24429,7 +24429,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25366,7 +25366,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -27240,7 +27240,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28177,7 +28177,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -29114,7 +29114,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31925,7 +31925,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32862,7 +32862,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33799,7 +33799,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34736,7 +34736,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -35673,7 +35673,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -36610,7 +36610,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -37547,7 +37547,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38484,7 +38484,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39421,7 +39421,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -40358,7 +40358,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -41295,7 +41295,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42232,7 +42232,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -43169,7 +43169,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -44109,7 +44109,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -44508,7 +44508,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -44904,7 +44904,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -45844,7 +45844,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -46243,7 +46243,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -46642,7 +46642,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -47041,7 +47041,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -47437,7 +47437,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -48377,7 +48377,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -48776,7 +48776,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -49175,7 +49175,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -49574,7 +49574,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -49973,7 +49973,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -50369,7 +50369,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51309,7 +51309,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -51708,7 +51708,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52107,7 +52107,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -52506,7 +52506,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -52902,7 +52902,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -53842,7 +53842,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -54241,7 +54241,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -54640,7 +54640,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55039,7 +55039,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -55435,7 +55435,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -56375,7 +56375,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -56774,7 +56774,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -57173,7 +57173,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -57572,7 +57572,7 @@
       </c>
       <c r="AJ302" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK302" t="inlineStr">
@@ -57971,7 +57971,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -58367,7 +58367,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -59307,7 +59307,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -59706,7 +59706,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -60105,7 +60105,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -60504,7 +60504,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -60900,7 +60900,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -61840,7 +61840,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -62239,7 +62239,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -62638,7 +62638,7 @@
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -63037,7 +63037,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -63433,7 +63433,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -64373,7 +64373,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -64772,7 +64772,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -65171,7 +65171,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -65570,7 +65570,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -65969,7 +65969,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -66365,7 +66365,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -67305,7 +67305,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -67704,7 +67704,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -68103,7 +68103,7 @@
       </c>
       <c r="AJ356" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK356" t="inlineStr">
@@ -68502,7 +68502,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -68898,7 +68898,7 @@
       </c>
       <c r="AJ360" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK360" t="inlineStr">
@@ -69838,7 +69838,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -70237,7 +70237,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -70636,7 +70636,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -71035,7 +71035,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -71434,7 +71434,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -71830,7 +71830,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -72770,7 +72770,7 @@
       </c>
       <c r="AJ380" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK380" t="inlineStr">
@@ -73169,7 +73169,7 @@
       </c>
       <c r="AJ382" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK382" t="inlineStr">
@@ -73568,7 +73568,7 @@
       </c>
       <c r="AJ384" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK384" t="inlineStr">
@@ -73967,7 +73967,7 @@
       </c>
       <c r="AJ386" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK386" t="inlineStr">
@@ -74363,7 +74363,7 @@
       </c>
       <c r="AJ388" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK388" t="inlineStr">
@@ -75303,7 +75303,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -75702,7 +75702,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -76101,7 +76101,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -76500,7 +76500,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -76896,7 +76896,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -77836,7 +77836,7 @@
       </c>
       <c r="AJ406" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK406" t="inlineStr">
@@ -78235,7 +78235,7 @@
       </c>
       <c r="AJ408" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK408" t="inlineStr">
@@ -78634,7 +78634,7 @@
       </c>
       <c r="AJ410" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK410" t="inlineStr">
@@ -79033,7 +79033,7 @@
       </c>
       <c r="AJ412" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK412" t="inlineStr">
@@ -79432,7 +79432,7 @@
       </c>
       <c r="AJ414" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK414" t="inlineStr">
@@ -79828,7 +79828,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -80768,7 +80768,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -81167,7 +81167,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -81566,7 +81566,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -81965,7 +81965,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
